--- a/src/assets/Flowtemp.xlsx
+++ b/src/assets/Flowtemp.xlsx
@@ -37,11 +37,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -71,10 +78,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -293,34 +311,35 @@
   <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" customWidth="1"/>
-    <col min="4" max="26" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" style="1" customWidth="1"/>
+    <col min="4" max="26" width="8.7109375" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1320,7 +1339,8 @@
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>